--- a/Dependencies/Takasugi_2024/dataset_metrics.xlsx
+++ b/Dependencies/Takasugi_2024/dataset_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58728</v>
+        <v>58435</v>
       </c>
       <c r="C2" t="n">
-        <v>44856</v>
+        <v>44404</v>
       </c>
       <c r="D2" t="n">
-        <v>44579</v>
+        <v>44377</v>
       </c>
       <c r="E2" t="n">
-        <v>41551</v>
+        <v>41341</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77308</v>
+        <v>76660</v>
       </c>
       <c r="C3" t="n">
-        <v>54118</v>
+        <v>53704</v>
       </c>
       <c r="D3" t="n">
-        <v>53683</v>
+        <v>53618</v>
       </c>
       <c r="E3" t="n">
-        <v>50762</v>
+        <v>50676</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40654</v>
+        <v>40195</v>
       </c>
       <c r="C4" t="n">
-        <v>34304</v>
+        <v>33982</v>
       </c>
       <c r="D4" t="n">
-        <v>34088</v>
+        <v>33942</v>
       </c>
       <c r="E4" t="n">
-        <v>31796</v>
+        <v>31658</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54589</v>
+        <v>54111</v>
       </c>
       <c r="C5" t="n">
-        <v>45865</v>
+        <v>45523</v>
       </c>
       <c r="D5" t="n">
-        <v>45567</v>
+        <v>45480</v>
       </c>
       <c r="E5" t="n">
-        <v>42587</v>
+        <v>42483</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69585</v>
+        <v>69138</v>
       </c>
       <c r="C6" t="n">
-        <v>46113</v>
+        <v>45767</v>
       </c>
       <c r="D6" t="n">
-        <v>45787</v>
+        <v>45685</v>
       </c>
       <c r="E6" t="n">
-        <v>42926</v>
+        <v>42803</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26592</v>
+        <v>26590</v>
       </c>
       <c r="C7" t="n">
-        <v>18995</v>
+        <v>18931</v>
       </c>
       <c r="D7" t="n">
-        <v>18886</v>
+        <v>18909</v>
       </c>
       <c r="E7" t="n">
-        <v>17182</v>
+        <v>17185</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74290</v>
+        <v>73354</v>
       </c>
       <c r="C8" t="n">
-        <v>56465</v>
+        <v>56159</v>
       </c>
       <c r="D8" t="n">
-        <v>56120</v>
+        <v>56109</v>
       </c>
       <c r="E8" t="n">
-        <v>51925</v>
+        <v>51893</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Takasugi_2024/dataset_metrics.xlsx
+++ b/Dependencies/Takasugi_2024/dataset_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,38 +553,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Muscle</t>
+          <t>Lung</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26590</v>
+        <v>50695</v>
       </c>
       <c r="C7" t="n">
-        <v>18931</v>
+        <v>45434</v>
       </c>
       <c r="D7" t="n">
-        <v>18909</v>
+        <v>45385</v>
       </c>
       <c r="E7" t="n">
-        <v>17185</v>
+        <v>42318</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Muscle</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26590</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18931</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18909</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17185</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Skin</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>73354</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
         <v>56159</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" t="n">
         <v>56109</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>51893</v>
       </c>
     </row>

--- a/Dependencies/Takasugi_2024/dataset_metrics.xlsx
+++ b/Dependencies/Takasugi_2024/dataset_metrics.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58435</v>
+        <v>119924</v>
       </c>
       <c r="C2" t="n">
-        <v>44404</v>
+        <v>58862</v>
       </c>
       <c r="D2" t="n">
-        <v>44377</v>
+        <v>58862</v>
       </c>
       <c r="E2" t="n">
-        <v>41341</v>
+        <v>55255</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76660</v>
+        <v>149476</v>
       </c>
       <c r="C3" t="n">
-        <v>53704</v>
+        <v>67819</v>
       </c>
       <c r="D3" t="n">
-        <v>53618</v>
+        <v>67819</v>
       </c>
       <c r="E3" t="n">
-        <v>50676</v>
+        <v>64295</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40195</v>
+        <v>82879</v>
       </c>
       <c r="C4" t="n">
-        <v>33982</v>
+        <v>45721</v>
       </c>
       <c r="D4" t="n">
-        <v>33942</v>
+        <v>45721</v>
       </c>
       <c r="E4" t="n">
-        <v>31658</v>
+        <v>42914</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54111</v>
+        <v>107513</v>
       </c>
       <c r="C5" t="n">
-        <v>45523</v>
+        <v>59778</v>
       </c>
       <c r="D5" t="n">
-        <v>45480</v>
+        <v>59778</v>
       </c>
       <c r="E5" t="n">
-        <v>42483</v>
+        <v>56117</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69138</v>
+        <v>135546</v>
       </c>
       <c r="C6" t="n">
-        <v>45767</v>
+        <v>57940</v>
       </c>
       <c r="D6" t="n">
-        <v>45685</v>
+        <v>57940</v>
       </c>
       <c r="E6" t="n">
-        <v>42803</v>
+        <v>54651</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50695</v>
+        <v>102188</v>
       </c>
       <c r="C7" t="n">
-        <v>45434</v>
+        <v>60038</v>
       </c>
       <c r="D7" t="n">
-        <v>45385</v>
+        <v>60038</v>
       </c>
       <c r="E7" t="n">
-        <v>42318</v>
+        <v>56508</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26590</v>
+        <v>63183</v>
       </c>
       <c r="C8" t="n">
-        <v>18931</v>
+        <v>27272</v>
       </c>
       <c r="D8" t="n">
-        <v>18909</v>
+        <v>27272</v>
       </c>
       <c r="E8" t="n">
-        <v>17185</v>
+        <v>25150</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73354</v>
+        <v>141222</v>
       </c>
       <c r="C9" t="n">
-        <v>56159</v>
+        <v>72645</v>
       </c>
       <c r="D9" t="n">
-        <v>56109</v>
+        <v>72645</v>
       </c>
       <c r="E9" t="n">
-        <v>51893</v>
+        <v>68275</v>
       </c>
     </row>
   </sheetData>
